--- a/reports/2026-09-19__daily-marker.xlsx
+++ b/reports/2026-09-19__daily-marker.xlsx
@@ -11,26 +11,28 @@
     <sheet name="Availability" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Booking curve" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Curve by hull gen" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Final payment" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Peer gap" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Earnings window" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cohort index" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Depletion" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Promo diff" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Promo reference" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Offer boundary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Inclusion value" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Peer gap" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Earnings window" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Cohort index" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Depletion" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Promo diff" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Promo reference" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$45:$G$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Index'!$A$46:$G$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Availability'!$A$15:$P$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Booking curve'!$A$23:$V$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Curve by hull gen'!$A$25:$V$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Final payment'!$A$17:$R$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Peer gap'!$A$18:$P$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Earnings window'!$A$11:$I$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Cohort index'!$A$18:$S$339</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Depletion'!$A$16:$U$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Promo diff'!$A$16:$R$186</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Promo reference'!$A$14:$Q$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Offer boundary'!$A$19:$X$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Inclusion value'!$A$13:$N$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Peer gap'!$A$18:$P$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Earnings window'!$A$11:$I$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Cohort index'!$A$18:$S$339</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Depletion'!$A$16:$U$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Promo diff'!$A$16:$R$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Promo reference'!$A$14:$Q$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -622,7 +624,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-19T06:48:00+00:00</t>
+          <t>2026-09-19T18:01:07+00:00</t>
         </is>
       </c>
     </row>
@@ -765,42 +767,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Final payment</t>
+          <t>Offer boundary</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>final-payment</t>
+          <t>offer-boundary</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>this scrape date</t>
+          <t>all scrape dates in the tier</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>COLLECTION SCOPE CHANGED BETWEEN DATES</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Do fares and sold-out share jump as sailings cross final payment? A cutoff SCAN, so the boundary is located rather than assumed. Check peer_own_jump_pct before reading any row: where the control jumps too, the cutoff has caught the calendar.</t>
+          <t>Price change on sailings that CROSSED final payment, each compared to itself days apart. The event is dated by NCL: its risk-free cancellation offer applies outside final payment, so losing it is the crossing. Calendar is fixed by construction, so no seasonal correction is needed.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Peer gap</t>
+          <t>Inclusion value</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>peer-gap</t>
+          <t>inclusion-value</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -809,7 +811,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -818,19 +820,19 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NCLH vs peer median pppn, per region and cabin category, on cruise-only rows.</t>
+          <t>What the prepaid-gratuities giveaway is worth as a share of the fare beside it. Fares are ours; the per-day rate is NCL's published schedule, dated and sourced on every row. A discount that never touches the advertised price.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Earnings window</t>
+          <t>Peer gap</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>earnings-window</t>
+          <t>peer-gap</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -839,7 +841,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -848,49 +850,49 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sailings departing inside the NCLH print window vs outside it. Split on sail date, not collection date.</t>
+          <t>NCLH vs peer median pppn, per region and cabin category, on cruise-only rows.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cohort index</t>
+          <t>Earnings window</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cohort-index</t>
+          <t>earnings-window</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>all scrape dates in the tier</t>
+          <t>this scrape date</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>321</v>
+        <v>36</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>COLLECTION SCOPE CHANGED BETWEEN DATES</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Since-inception index on a MATCHED BASKET of cabins, with the naive all-rows index beside it. index_matched cannot be moved by sailings entering the book; mix_effect_pp is how much of the naive move is composition rather than price.</t>
+          <t>Sailings departing inside the NCLH print window vs outside it. Split on sail date, not collection date.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Depletion</t>
+          <t>Cohort index</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>depletion</t>
+          <t>cohort-index</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -899,7 +901,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>32</v>
+        <v>321</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -908,19 +910,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Change in closed share per day. Needs &gt;=2 collection dates or it reports nothing rather than inventing a slope.</t>
+          <t>Since-inception index on a MATCHED BASKET of cabins, with the naive all-rows index beside it. index_matched cannot be moved by sailings entering the book; mix_effect_pp is how much of the naive move is composition rather than price.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Promo diff</t>
+          <t>Depletion</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>promo-diff</t>
+          <t>depletion</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -929,7 +931,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>170</v>
+        <v>32</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -938,180 +940,190 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Which offers widened, narrowed, appeared or were withdrawn between dates, by reach on cabins seen both times.</t>
+          <t>Change in closed share per day. Needs &gt;=2 collection dates or it reports nothing rather than inventing a slope.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Promo diff</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>promo-diff</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>all scrape dates in the tier</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>170</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>COLLECTION SCOPE CHANGED BETWEEN DATES</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Which offers widened, narrowed, appeared or were withdrawn between dates, by reach on cabins seen both times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Promo reference</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>promo-reference</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>reference (every date in the tier)</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>19</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>The decoder ring: every offer observed, in the vendor's own words, with its reach and scope. Read the Promo diff against this rather than against a hash.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Region coverage on this basis</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Every region the config asks for, including those that returned nothing. A region with 0 rows is absent from every sheet; without this table that is indistinguishable from a region nobody requested.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>observations</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>sailings</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>lines</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>package_rows</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1040</v>
-      </c>
-      <c r="C35" t="n">
-        <v>205</v>
-      </c>
-      <c r="D35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" t="n">
-        <v>126</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>65</v>
+        <v>1040</v>
       </c>
       <c r="C36" t="n">
-        <v>11</v>
+        <v>205</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Bermuda</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Bermuda</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="C39" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -1121,174 +1133,2894 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>64</v>
+      </c>
+      <c r="C40" t="n">
+        <v>13</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Transatlantic</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="inlineStr">
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>no rows on this basis -- absent from every sheet</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Scope comparability between collection dates</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Whether each pair of adjacent collection dates sampled the same population. Where `comparable` is NO, the collector itself changed, and every slope or index spanning that pair is measuring the change to the collector as well as the market.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>from_date</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>to_date</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>sailings_before</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>sailings_after</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>sailings_delta_pct</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>comparable</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>why_not</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>113</v>
-      </c>
-      <c r="D46" t="n">
-        <v>126</v>
-      </c>
-      <c r="E46" s="6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
       <c r="C47" t="n">
+        <v>113</v>
+      </c>
+      <c r="D47" t="n">
         <v>126</v>
       </c>
-      <c r="D47" t="n">
-        <v>262</v>
-      </c>
       <c r="E47" s="6" t="n">
-        <v>107.9</v>
+        <v>11.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>sail window moved 2026-10-01..2026-12-31 -&gt; 2026-09-19..2027-05-16; regions added: Alaska; sailing count moved +107.9% (126 -&gt; 262)</t>
-        </is>
-      </c>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="n">
+        <v>126</v>
+      </c>
+      <c r="D48" t="n">
+        <v>262</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>sail window moved 2026-10-01..2026-12-31 -&gt; 2026-09-19..2027-05-16; regions added: Alaska; sailing count moved +107.9% (126 -&gt; 262)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C49" t="n">
         <v>262</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D49" t="n">
         <v>239</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E49" s="6" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>sail window moved 2026-09-19..2027-05-16 -&gt; 2026-09-20..2027-05-16</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A45:G48"/>
+  <autoFilter ref="A46:G49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Depletion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Change in closed share per day. Needs &gt;=2 collection dates or it reports nothing rather than inventing a slope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Time scope: all scrape dates in the tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>[daily-marker] sail 2026-09-19..2027-05-16 | regions: Alaska, Bermuda, Caribbean, Northern Europe, Southern Europe | observed 2026-09-16..2026-09-19 | 3657 obs / 399 sailings | granularity: category</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>! daily-marker is the Oct-Dec 2026 near-term cohort, and its region mix is set by seasonal deployment, not by sampling choice. Measured from the near-term universe on 2026-09-15: Caribbean 104 eligible itineraries (85 NCL / 19 Carnival); Southern Europe 15, ALL NCL, all departing October-early November, 0 in December and 0 on Carnival; Alaska 0. So cross-line work in this tier is Caribbean-only, and its Southern Europe rows are a single-line October series that dies when the Mediterranean season ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>! PEER-COMPARABLE REGIONS in this basis: Alaska, Bermuda, Caribbean, Southern Europe. Single-line only (no peer rows, so no cross-line claim can rest on them): Northern Europe (Norwegian Cruise Line).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>! COLLECTION SCOPE CHANGED BETWEEN DATES, so any movement here is partly the collector and not the market. A time series assumes each date sampled the same population; on 2 adjacent pair(s) it did not -- 2026-09-17-&gt;2026-09-18: sail window moved 2026-10-01..2026-12-31 -&gt; 2026-09-19..2027-05-16; regions added: Alaska; sailing count moved +107.9% (126 -&gt; 262); 2026-09-18-&gt;2026-09-19: sail window moved 2026-09-19..2027-05-16 -&gt; 2026-09-20..2027-05-16. Treat every slope and index spanning those dates as uninterpretable until a run of stable-scope dates exists. The per-row cell counts show the size of the break.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>- COMMON SUPPORT: both shares are computed over the same cells -- those observed on the first AND last date. Cells that entered in between cannot move the slope, so a widened collection scope cannot be read as depletion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>- closed share = (limited + sold_out) / bookable cells; solo_only is a product restriction, not scarcity, and is excluded from both sides.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>- dropped_cells left the book entirely (sailed, or delisted). That is not the same event as selling out and is reported, never folded in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>- newly_closed_cells / reopened_cells are the gross flows behind the net delta: a flat share can hide both.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>- naive_* is the unrestricted computation over whatever each date returned. mix_effect_pp = (naive delta - matched delta) in points.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>- Endpoint difference, not a fit: with few collection dates a regression would overstate precision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>cabin_category</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>first_date</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>last_date</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>matched_cells</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>first_closed_share</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>last_closed_share</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>delta_closed_share</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>closed_share_per_day</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>newly_closed_cells</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>reopened_cells</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>dropped_cells</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>entered_cells</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>naive_first_closed_share</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="inlineStr">
+        <is>
+          <t>naive_last_closed_share</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>naive_delta</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr">
+        <is>
+          <t>mix_effect_pp</t>
+        </is>
+      </c>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>observations</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>balcony</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" s="9" t="inlineStr">
+        <is>
+          <t>VERY THIN (n=7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" s="9" t="inlineStr">
+        <is>
+          <t>VERY THIN (n=7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>oceanview</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" s="9" t="inlineStr">
+        <is>
+          <t>VERY THIN (n=7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" s="9" t="inlineStr">
+        <is>
+          <t>VERY THIN (n=7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>balcony</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (n=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (n=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>oceanview</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (n=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (n=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>balcony</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>11</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>52</v>
+      </c>
+      <c r="O25" t="n">
+        <v>114</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-0.0236</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-11.45</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>52</v>
+      </c>
+      <c r="O26" t="n">
+        <v>114</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>oceanview</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>11</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>52</v>
+      </c>
+      <c r="O27" t="n">
+        <v>114</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-7.47</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Carnival Cruise Line</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>11</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>52</v>
+      </c>
+      <c r="O28" t="n">
+        <v>114</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v>0.2381</v>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-0.1741</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-17.41</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>balcony</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>10</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="S29" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="S30" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" s="9" t="inlineStr">
+        <is>
+          <t>VERY THIN (n=5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>oceanview</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="S31" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" s="9" t="inlineStr">
+        <is>
+          <t>VERY THIN (n=5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-0.1667</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" s="9" t="inlineStr">
+        <is>
+          <t>VERY THIN (n=5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>balcony</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>6</v>
+      </c>
+      <c r="O33" t="n">
+        <v>10</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="R33" t="n">
+        <v>-0.0208</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-18.75</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" s="9" t="inlineStr">
+        <is>
+          <t>VERY THIN (n=6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4</v>
+      </c>
+      <c r="O34" t="n">
+        <v>10</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-0.1667</v>
+      </c>
+      <c r="S34" t="n">
+        <v>-16.67</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (n=3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>oceanview</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3</v>
+      </c>
+      <c r="O35" t="n">
+        <v>5</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-0.1667</v>
+      </c>
+      <c r="S35" t="n">
+        <v>-16.67</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (n=3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>6</v>
+      </c>
+      <c r="O36" t="n">
+        <v>5</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-0.3333</v>
+      </c>
+      <c r="S36" t="n">
+        <v>-33.33</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (n=3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>balcony</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>38</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>16</v>
+      </c>
+      <c r="O37" t="n">
+        <v>122</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="R37" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="S37" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=38)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>38</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>16</v>
+      </c>
+      <c r="O38" t="n">
+        <v>122</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>oceanview</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" t="n">
+        <v>19</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>8</v>
+      </c>
+      <c r="O39" t="n">
+        <v>61</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" t="n">
+        <v>31</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>13</v>
+      </c>
+      <c r="O40" t="n">
+        <v>109</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="R40" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="S40" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" s="9" t="inlineStr">
+        <is>
+          <t>ok (n=31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Northern Europe</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>balcony</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>-0.16667</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (n=2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Northern Europe</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (n=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Northern Europe</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>oceanview</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (n=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Northern Europe</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (n=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>balcony</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" t="n">
+        <v>14</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>0.2143</v>
+      </c>
+      <c r="I45" s="6" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="J45" s="6" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="K45" s="6" t="n">
+        <v>0.02381</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>14</v>
+      </c>
+      <c r="O45" t="n">
+        <v>8</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v>0.2143</v>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v>0.2273</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="S45" t="n">
+        <v>-5.84</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" t="n">
+        <v>10</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>9</v>
+      </c>
+      <c r="O46" t="n">
+        <v>6</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" s="9" t="inlineStr">
+        <is>
+          <t>VERY THIN (n=7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>oceanview</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" t="n">
+        <v>7</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="J47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>7</v>
+      </c>
+      <c r="O47" t="n">
+        <v>4</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="R47" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="S47" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" s="9" t="inlineStr">
+        <is>
+          <t>VERY THIN (n=7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Norwegian Cruise Line</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" t="n">
+        <v>11</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>8</v>
+      </c>
+      <c r="O48" t="n">
+        <v>5</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" s="10" t="inlineStr">
+        <is>
+          <t>THIN (n=11)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A16:U48"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14086,7 +16818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24043,54 +26775,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:X22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="17" customWidth="1" min="17" max="17"/>
-    <col width="46" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="25" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Final payment</t>
+          <t>Offer boundary</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Do fares and sold-out share jump as sailings cross final payment? A cutoff SCAN, so the boundary is located rather than assumed. Check peer_own_jump_pct before reading any row: where the control jumps too, the cutoff has caught the calendar.</t>
+          <t>Price change on sailings that CROSSED final payment, each compared to itself days apart. The event is dated by NCL: its risk-free cancellation offer applies outside final payment, so losing it is the crossing. Calendar is fixed by construction, so no seasonal correction is needed.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Time scope: this scrape date.</t>
+          <t>Time scope: all scrape dates in the tier.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>[daily-marker] sail 2026-09-20..2027-05-16 | regions: Caribbean | observed 2026-09-19 | 428 obs / 122 sailings | granularity: category</t>
+          <t>[daily-marker] sail 2026-09-19..2027-05-16 | regions: Alaska, Bermuda, Caribbean, Northern Europe, Southern Europe | observed 2026-09-16..2026-09-19 | 2392 obs / 384 sailings | granularity: category</t>
         </is>
       </c>
     </row>
@@ -24104,1738 +26842,1026 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>! PEER-COMPARABLE REGIONS in this basis: Caribbean. Single-line only (no peer rows, so no cross-line claim can rest on them): none.</t>
+          <t>! PEER-COMPARABLE REGIONS in this basis: Alaska, Bermuda, Caribbean, Southern Europe. Single-line only (no peer rows, so no cross-line claim can rest on them): Northern Europe (Norwegian Cruise Line).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>! COVERAGE: no Southern Europe rows in this tier. Southern Europe evidence must come from weekly-full and be reported separately.</t>
+          <t>! ONLY 1 CROSSING(S) OBSERVED. The mechanism is visible but the estimate is not yet worth quoting: one day's worth of sailings crosses the boundary per day, so the sample grows by a few events per collection date and no faster.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>! SINGLE-REGION BASIS: every row here is Caribbean. Do not generalise this to the other regions in the panel.</t>
+          <t>! COLLECTION SCOPE CHANGED BETWEEN DATES, so any movement here is partly the collector and not the market. A time series assumes each date sampled the same population; on 2 adjacent pair(s) it did not -- 2026-09-17-&gt;2026-09-18: sail window moved 2026-10-01..2026-12-31 -&gt; 2026-09-19..2027-05-16; regions added: Alaska; sailing count moved +107.9% (126 -&gt; 262); 2026-09-18-&gt;2026-09-19: sail window moved 2026-09-19..2027-05-16 -&gt; 2026-09-20..2027-05-16. Treat every slope and index spanning those dates as uninterpretable until a run of stable-scope dates exists. The per-row cell counts show the size of the break.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>! CUTOFF SCAN: several candidate boundaries are reported so the break can be located rather than assumed. Reading only the row that suits the argument is p-hacking; report the profile.</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>- Event = a sailing carrying 'Risk-Free-Cancellation-Offer' on one collection date and not on the next. NCL defines that offer as applying to sailings still outside final payment, so its loss IS the crossing, dated by the vendor rather than assumed by us.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>- Windows are [C-30, C) inside final payment and [C, C+30) outside it, on days to departure.</t>
+          <t>- EACH SAILING IS COMPARED TO ITSELF days apart, so the calendar is held fixed by construction. This is why it needs no seasonal correction, and why it works where the cross-sectional cutoff scan could not be identified.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>- price_jump_pct is inside minus outside: a line that discounts once the money is committed reads NEGATIVE.</t>
+          <t>- Price change is a matched basket: only cabin grades priced on BOTH dates, so a cabin selling out cannot read as a price move.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>- did_* subtract the peer's own jump at the same cutoff. That is the control, and it only works while the peer's OWN final-payment boundary lies outside both windows -- peer_own_jump_pct is there to be checked, not decoration.</t>
+          <t>- kept_offer is the control that matters -- same line, same days, still outside the boundary. peer_same_lead catches an industry-wide move.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>- SEASONALITY IS THE BINDING CONSTRAINT. On a single collection date days-to-departure is a one-to-one map onto the calendar, so the two windows are always different weeks of the year. Where a cutoff puts the holiday peak on one side, BOTH lines jump and the discontinuity is the calendar, not final payment. `inside_sails` / `outside_sails` and `peer_own_jump_pct` are there to catch exactly that.</t>
+          <t>- READ share_cut AND p_vs_*, NOT THE MEDIAN. Fares are sticky day to day, so most cabins contribute a zero and the median is dominated by them. The frequency of cutting is the informative statistic, and p_vs_kept / p_vs_peer are exact binomial tails against each control group's own cut rate over the same windows.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>- A discontinuity on one collection date is suggestive. The same sailings observed weekly AS they cross the boundary is the stronger test, and the panel accumulates toward it.</t>
+          <t>- ONSET, NOT SIZE. This measures what happens in the days right after a sailing crosses the boundary -- where cutting STARTS. It is not the total discount, and must not be read as the yield hit. The booking curve shows where it ends, tens of index points lower by 30-44 days out. Two exhibits, one mechanism, different horizons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>- The control rows are a finding in their own right: share_cut on kept_offer against peer_same_lead is how often each line reprices AWAY from the boundary at all.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>cutoff_days</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>n_inside</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>n_outside</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>inside_sails</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>outside_sails</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>median_inside</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>median_outside</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>price_jump_pct</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>sold_out_inside</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>sold_out_outside</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>sold_out_jump_pp</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>promo_inside</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="inlineStr">
-        <is>
-          <t>promo_outside</t>
-        </is>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>peer_own_jump_pct</t>
-        </is>
-      </c>
-      <c r="P17" s="5" t="inlineStr">
-        <is>
-          <t>did_price_pct</t>
-        </is>
-      </c>
-      <c r="Q17" s="5" t="inlineStr">
-        <is>
-          <t>did_sold_out_pp</t>
-        </is>
-      </c>
-      <c r="R17" s="5" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>- A COLLECTION-SCOPE WARNING ON THIS SHEET IS OVER-CAUTIOUS. Only sailings present on BOTH dates enter, and each is compared to itself, so a changed marker list or widened window costs events but cannot bias the measured change. Read the event count, not the drift flag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>sailings</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>matched_cabins</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>median_change_pct</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>mean_change_pct</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>p25_change_pct</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>p75_change_pct</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>share_cut</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>sold_out_change_pp</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>median_lead_days</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>ships</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>itineraries</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>crossing_windows</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>sail_from</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="inlineStr">
+        <is>
+          <t>sail_to</t>
+        </is>
+      </c>
+      <c r="Q19" s="5" t="inlineStr">
+        <is>
+          <t>vs_kept_pp</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="inlineStr">
+        <is>
+          <t>vs_peer_pp</t>
+        </is>
+      </c>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>cut_of_n</t>
+        </is>
+      </c>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>base_rate_kept</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>base_rate_peer</t>
+        </is>
+      </c>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>p_vs_kept</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="inlineStr">
+        <is>
+          <t>p_vs_peer</t>
+        </is>
+      </c>
+      <c r="X19" s="5" t="inlineStr">
         <is>
           <t>sample</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>None..None</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>None..None</t>
-        </is>
-      </c>
-      <c r="O18" s="6" t="n">
-        <v>-4</v>
-      </c>
-      <c r="R18" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-20..2026-10-03</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-10-10..2026-10-31</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>130.53</v>
-      </c>
-      <c r="H19" t="n">
-        <v>136</v>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.1333</v>
-      </c>
-      <c r="L19" t="n">
-        <v>53.33</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=2)</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>30</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ALL PAIRS POOLED</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Norwegian Cruise Line</t>
+          <t>kept_offer</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>None..None</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-11-07..2026-11-15</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>113.43</v>
+        <v>138</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>176</v>
+      </c>
+      <c r="L20" t="n">
+        <v>7</v>
+      </c>
+      <c r="M20" t="n">
+        <v>7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O20" s="6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=0)</t>
+        <v>1</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2027-01-22</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2027-05-16</t>
+        </is>
+      </c>
+      <c r="X20" s="9" t="inlineStr">
+        <is>
+          <t>control (n=46)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>30</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ALL PAIRS POOLED</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>lost_offer</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-20..2026-10-17</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-10-24..2026-11-15</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>139.71</v>
-      </c>
-      <c r="H21" t="n">
-        <v>127.62</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>9.5</v>
+        <v>3</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="L21" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=4)</t>
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2027-01-17</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2027-01-17</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+      <c r="T21" s="6" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="U21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (events=1)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>45</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ALL PAIRS POOLED</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Norwegian Cruise Line</t>
+          <t>peer_same_lead</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>None..None</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-11-07..2026-11-29</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>113.43</v>
+        <v>51</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>113</v>
+      </c>
+      <c r="L22" t="n">
+        <v>6</v>
+      </c>
+      <c r="M22" t="n">
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O22" s="6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>45</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>5</v>
-      </c>
-      <c r="D23" t="n">
-        <v>9</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-10-10..2026-10-31</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-11-07..2026-11-29</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>136</v>
-      </c>
-      <c r="H23" t="n">
-        <v>132.29</v>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.1333</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>60</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" t="n">
-        <v>12</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-11-07..2026-11-15</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-11-20..2026-12-13</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>113.43</v>
-      </c>
-      <c r="H24" t="n">
-        <v>107</v>
-      </c>
-      <c r="I24" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O24" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P24" s="8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>60</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>7</v>
-      </c>
-      <c r="D25" t="n">
-        <v>7</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-10-24..2026-11-15</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-11-21..2026-12-13</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>127.62</v>
-      </c>
-      <c r="H25" t="n">
-        <v>122.29</v>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>75</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>10</v>
-      </c>
-      <c r="D26" t="n">
-        <v>11</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-11-07..2026-11-29</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-12-04..2026-12-30</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>113.43</v>
-      </c>
-      <c r="H26" t="n">
-        <v>127</v>
-      </c>
-      <c r="I26" s="8" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O26" s="6" t="n">
-        <v>-30</v>
-      </c>
-      <c r="P26" s="8" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="10" t="inlineStr">
-        <is>
-          <t>THIN (min side=10); CONTROL ALSO JUMPS, did not identified</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>75</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>9</v>
-      </c>
-      <c r="D27" t="n">
-        <v>7</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-11-07..2026-11-29</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-12-05..2026-12-27</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>132.29</v>
-      </c>
-      <c r="H27" t="n">
-        <v>188.88</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>-30</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>90</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>12</v>
-      </c>
-      <c r="D28" t="n">
-        <v>11</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-11-20..2026-12-13</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-12-19..2027-01-16</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>107</v>
-      </c>
-      <c r="H28" t="n">
-        <v>161.29</v>
-      </c>
-      <c r="I28" s="8" t="n">
-        <v>-33.7</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O28" s="6" t="n">
-        <v>-18.9</v>
-      </c>
-      <c r="P28" s="8" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="10" t="inlineStr">
-        <is>
-          <t>THIN (min side=11); CONTROL ALSO JUMPS, did not identified</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>90</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>7</v>
-      </c>
-      <c r="D29" t="n">
-        <v>9</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2026-11-21..2026-12-13</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-12-18..2027-01-16</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>122.29</v>
-      </c>
-      <c r="H29" t="n">
-        <v>150.75</v>
-      </c>
-      <c r="I29" s="8" t="n">
-        <v>-18.9</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>105</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>11</v>
-      </c>
-      <c r="D30" t="n">
-        <v>13</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2026-12-04..2026-12-30</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2027-01-02..2027-01-31</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>127</v>
-      </c>
-      <c r="H30" t="n">
-        <v>144.14</v>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O30" s="6" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="P30" s="8" t="n">
-        <v>-90.2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="10" t="inlineStr">
-        <is>
-          <t>THIN (min side=11); CONTROL ALSO JUMPS, did not identified</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>105</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>7</v>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2026-12-05..2026-12-27</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2027-01-02..2027-01-31</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>188.88</v>
-      </c>
-      <c r="H31" t="n">
-        <v>105.93</v>
-      </c>
-      <c r="I31" s="8" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>120</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>11</v>
-      </c>
-      <c r="D32" t="n">
-        <v>13</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2026-12-19..2027-01-16</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2027-01-17..2027-02-14</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>161.29</v>
-      </c>
-      <c r="H32" t="n">
-        <v>150.71</v>
-      </c>
-      <c r="I32" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O32" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>-27</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="10" t="inlineStr">
-        <is>
-          <t>THIN (min side=11); CONTROL ALSO JUMPS, did not identified</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>120</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>9</v>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-12-18..2027-01-16</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2027-01-23..2027-02-13</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>150.75</v>
-      </c>
-      <c r="H33" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="I33" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>135</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>13</v>
-      </c>
-      <c r="D34" t="n">
-        <v>12</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2027-01-02..2027-01-31</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2027-02-05..2027-02-28</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>144.14</v>
-      </c>
-      <c r="H34" t="n">
-        <v>150.21</v>
-      </c>
-      <c r="I34" s="8" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O34" s="6" t="n">
-        <v>-10.9</v>
-      </c>
-      <c r="P34" s="8" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="10" t="inlineStr">
-        <is>
-          <t>THIN (min side=12); CONTROL ALSO JUMPS, did not identified</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>135</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>10</v>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2027-01-02..2027-01-31</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2027-02-06..2027-02-28</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>105.93</v>
-      </c>
-      <c r="H35" t="n">
-        <v>118.86</v>
-      </c>
-      <c r="I35" s="8" t="n">
-        <v>-10.9</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="10" t="inlineStr">
-        <is>
-          <t>THIN (min side=10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>150</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>13</v>
-      </c>
-      <c r="D36" t="n">
-        <v>12</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2027-01-17..2027-02-14</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2027-02-19..2027-03-14</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>150.71</v>
-      </c>
-      <c r="H36" t="n">
-        <v>149</v>
-      </c>
-      <c r="I36" s="8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O36" s="6" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="P36" s="8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="10" t="inlineStr">
-        <is>
-          <t>THIN (min side=12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>150</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>10</v>
-      </c>
-      <c r="D37" t="n">
-        <v>8</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2027-01-23..2027-02-13</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2027-02-20..2027-03-13</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="H37" t="n">
-        <v>116.57</v>
-      </c>
-      <c r="I37" s="8" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>165</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>12</v>
-      </c>
-      <c r="D38" t="n">
-        <v>12</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2027-02-05..2027-02-28</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2027-03-05..2027-03-28</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>150.21</v>
-      </c>
-      <c r="H38" t="n">
-        <v>159.07</v>
-      </c>
-      <c r="I38" s="8" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O38" s="6" t="n">
-        <v>-24.2</v>
-      </c>
-      <c r="P38" s="8" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" s="10" t="inlineStr">
-        <is>
-          <t>THIN (min side=12); CONTROL ALSO JUMPS, did not identified</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>165</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>10</v>
-      </c>
-      <c r="D39" t="n">
-        <v>7</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2027-02-06..2027-02-28</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2027-03-06..2027-03-27</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>118.86</v>
-      </c>
-      <c r="H39" t="n">
-        <v>156.86</v>
-      </c>
-      <c r="I39" s="8" t="n">
-        <v>-24.2</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>180</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>12</v>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2027-02-19..2027-03-14</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2027-03-19..2027-04-11</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>149</v>
-      </c>
-      <c r="H40" t="n">
-        <v>166.21</v>
-      </c>
-      <c r="I40" s="8" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O40" s="6" t="n">
-        <v>-17.7</v>
-      </c>
-      <c r="P40" s="8" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="10" t="inlineStr">
-        <is>
-          <t>THIN (min side=10); CONTROL ALSO JUMPS, did not identified</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>180</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>8</v>
-      </c>
-      <c r="D41" t="n">
-        <v>9</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2027-02-20..2027-03-13</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2027-03-20..2027-04-10</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>116.57</v>
-      </c>
-      <c r="H41" t="n">
-        <v>141.62</v>
-      </c>
-      <c r="I41" s="8" t="n">
-        <v>-17.7</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>195</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>12</v>
-      </c>
-      <c r="D42" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2027-03-05..2027-03-28</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2027-04-02..2027-04-11</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>159.07</v>
-      </c>
-      <c r="H42" t="n">
-        <v>167</v>
-      </c>
-      <c r="I42" s="8" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O42" s="6" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="P42" s="8" t="n">
-        <v>-25.9</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=4); CONTROL ALSO JUMPS, did not identified</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>195</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>7</v>
-      </c>
-      <c r="D43" t="n">
-        <v>9</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2027-03-06..2027-03-27</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2027-04-03..2027-04-24</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>156.86</v>
-      </c>
-      <c r="H43" t="n">
-        <v>129.43</v>
-      </c>
-      <c r="I43" s="8" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>210</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>10</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2027-03-19..2027-04-11</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>None..None</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>166.21</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O44" s="6" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="R44" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>210</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>9</v>
-      </c>
-      <c r="D45" t="n">
-        <v>6</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2027-03-20..2027-04-10</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2027-04-17..2027-05-16</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>141.62</v>
-      </c>
-      <c r="H45" t="n">
-        <v>131</v>
-      </c>
-      <c r="I45" s="8" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (min side=6)</t>
+        <v>3</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-12-26</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2027-02-06</t>
+        </is>
+      </c>
+      <c r="X22" s="9" t="inlineStr">
+        <is>
+          <t>control (n=17)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A17:R45"/>
+  <autoFilter ref="A19:X22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Inclusion value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>What the prepaid-gratuities giveaway is worth as a share of the fare beside it. Fares are ours; the per-day rate is NCL's published schedule, dated and sourced on every row. A discount that never touches the advertised price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Time scope: this scrape date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>[daily-marker] sail 2026-09-27..2027-05-16 | regions: Alaska, Bermuda, Caribbean, Northern Europe, Southern Europe | observed 2026-09-19 | 469 obs / 87 sailings | granularity: category</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>! daily-marker is the Oct-Dec 2026 near-term cohort, and its region mix is set by seasonal deployment, not by sampling choice. Measured from the near-term universe on 2026-09-15: Caribbean 104 eligible itineraries (85 NCL / 19 Carnival); Southern Europe 15, ALL NCL, all departing October-early November, 0 in December and 0 on Carnival; Alaska 0. So cross-line work in this tier is Caribbean-only, and its Southern Europe rows are a single-line October series that dies when the Mediterranean season ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>! HALF MEASURED, HALF CITED: fares are this panel's own observations; the per-day rate is Norwegian Cruise Line's published schedule as of 2026-09-19 (NCL published service-charge schedule (company FAQ)), which we did not observe. Press has reported increases; verify the current rate before quoting a discount figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>- effective_discount_pct = rate per person per DAY / fare per person per NIGHT. Itinerary length cancels, so the percentage is comparable across 4-night and 11-night sailings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>- The suite rate is applied only where a group is entirely suites; a mixed group takes the lower default rate, which understates rather than flatters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>- This is a discount that never touches the advertised price, which is why an advertised-price tracker registers nothing while it runs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>- Reach, targeting and sail window are measured by promo_reference and promo_diff; only the per-day rate comes from outside the panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>cabin_category</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>cells_with_offer</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>sailings</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>ships</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>median_pppn_observed</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>median_nights</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>rate_per_person_per_day</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>effective_discount_pct</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>value_per_person</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>fare_per_person</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>rate_as_of</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>rate_source</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>balcony</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>269.14</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>140</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>1884</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>NCL published service-charge schedule (company FAQ)</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (cells=8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>711.29</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>175</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>4979</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>NCL published service-charge schedule (company FAQ)</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (cells=4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>balcony</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>202</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>140</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>1414</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>NCL published service-charge schedule (company FAQ)</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>THIN (cells=10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>508.43</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>175</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>3559</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>NCL published service-charge schedule (company FAQ)</t>
+        </is>
+      </c>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (cells=5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>balcony</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>100</v>
+      </c>
+      <c r="D18" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>207</v>
+      </c>
+      <c r="G18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>140</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>1449</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>NCL published service-charge schedule (company FAQ)</t>
+        </is>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>ok (cells=100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Caribbean</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>81</v>
+      </c>
+      <c r="D19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>514.14</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>175</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>3599</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>NCL published service-charge schedule (company FAQ)</t>
+        </is>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>ok (cells=81)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>balcony</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>391.1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>140</v>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>2737.69</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>NCL published service-charge schedule (company FAQ)</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (cells=6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Southern Europe</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>suite</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>670.88</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>250</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>6708.79</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>NCL published service-charge schedule (company FAQ)</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT (cells=4)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A13:N21"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26845,7 +28871,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28111,7 +30137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -51735,2704 +53761,4 @@
   <autoFilter ref="A18:S339"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U48"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Depletion</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Change in closed share per day. Needs &gt;=2 collection dates or it reports nothing rather than inventing a slope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Time scope: all scrape dates in the tier.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>[daily-marker] sail 2026-09-19..2027-05-16 | regions: Alaska, Bermuda, Caribbean, Northern Europe, Southern Europe | observed 2026-09-16..2026-09-19 | 3657 obs / 399 sailings | granularity: category</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>! daily-marker is the Oct-Dec 2026 near-term cohort, and its region mix is set by seasonal deployment, not by sampling choice. Measured from the near-term universe on 2026-09-15: Caribbean 104 eligible itineraries (85 NCL / 19 Carnival); Southern Europe 15, ALL NCL, all departing October-early November, 0 in December and 0 on Carnival; Alaska 0. So cross-line work in this tier is Caribbean-only, and its Southern Europe rows are a single-line October series that dies when the Mediterranean season ends.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>! PEER-COMPARABLE REGIONS in this basis: Alaska, Bermuda, Caribbean, Southern Europe. Single-line only (no peer rows, so no cross-line claim can rest on them): Northern Europe (Norwegian Cruise Line).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>! COLLECTION SCOPE CHANGED BETWEEN DATES, so any movement here is partly the collector and not the market. A time series assumes each date sampled the same population; on 2 adjacent pair(s) it did not -- 2026-09-17-&gt;2026-09-18: sail window moved 2026-10-01..2026-12-31 -&gt; 2026-09-19..2027-05-16; regions added: Alaska; sailing count moved +107.9% (126 -&gt; 262); 2026-09-18-&gt;2026-09-19: sail window moved 2026-09-19..2027-05-16 -&gt; 2026-09-20..2027-05-16. Treat every slope and index spanning those dates as uninterpretable until a run of stable-scope dates exists. The per-row cell counts show the size of the break.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>- COMMON SUPPORT: both shares are computed over the same cells -- those observed on the first AND last date. Cells that entered in between cannot move the slope, so a widened collection scope cannot be read as depletion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>- closed share = (limited + sold_out) / bookable cells; solo_only is a product restriction, not scarcity, and is excluded from both sides.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>- dropped_cells left the book entirely (sailed, or delisted). That is not the same event as selling out and is reported, never folded in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>- newly_closed_cells / reopened_cells are the gross flows behind the net delta: a flat share can hide both.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>- naive_* is the unrestricted computation over whatever each date returned. mix_effect_pp = (naive delta - matched delta) in points.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>- Endpoint difference, not a fit: with few collection dates a regression would overstate precision.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>region</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>cabin_category</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>first_date</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>last_date</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>matched_cells</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>first_closed_share</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>last_closed_share</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>delta_closed_share</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>closed_share_per_day</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>newly_closed_cells</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>reopened_cells</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>dropped_cells</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>entered_cells</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="inlineStr">
-        <is>
-          <t>naive_first_closed_share</t>
-        </is>
-      </c>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>naive_last_closed_share</t>
-        </is>
-      </c>
-      <c r="R16" s="5" t="inlineStr">
-        <is>
-          <t>naive_delta</t>
-        </is>
-      </c>
-      <c r="S16" s="5" t="inlineStr">
-        <is>
-          <t>mix_effect_pp</t>
-        </is>
-      </c>
-      <c r="T16" s="5" t="inlineStr">
-        <is>
-          <t>observations</t>
-        </is>
-      </c>
-      <c r="U16" s="5" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Alaska</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>balcony</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>7</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" s="9" t="inlineStr">
-        <is>
-          <t>VERY THIN (n=7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Alaska</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" s="9" t="inlineStr">
-        <is>
-          <t>VERY THIN (n=7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Alaska</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>oceanview</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" s="9" t="inlineStr">
-        <is>
-          <t>VERY THIN (n=7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Alaska</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>suite</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>7</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>0.1429</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>0.1429</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v>0.1429</v>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v>0.1429</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" s="9" t="inlineStr">
-        <is>
-          <t>VERY THIN (n=7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>balcony</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (n=1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (n=1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>oceanview</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (n=1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>suite</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (n=1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>balcony</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" t="n">
-        <v>11</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>0.09089999999999999</v>
-      </c>
-      <c r="J25" s="6" t="n">
-        <v>0.09089999999999999</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>0.0303</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>52</v>
-      </c>
-      <c r="O25" t="n">
-        <v>114</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v>0.0476</v>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="R25" t="n">
-        <v>-0.0236</v>
-      </c>
-      <c r="S25" t="n">
-        <v>-11.45</v>
-      </c>
-      <c r="T25" t="n">
-        <v>4</v>
-      </c>
-      <c r="U25" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>3</v>
-      </c>
-      <c r="G26" t="n">
-        <v>11</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>52</v>
-      </c>
-      <c r="O26" t="n">
-        <v>114</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>4</v>
-      </c>
-      <c r="U26" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>oceanview</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" t="n">
-        <v>11</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>0.09089999999999999</v>
-      </c>
-      <c r="J27" s="6" t="n">
-        <v>0.09089999999999999</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>0.0303</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>52</v>
-      </c>
-      <c r="O27" t="n">
-        <v>114</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v>0.0317</v>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.0163</v>
-      </c>
-      <c r="S27" t="n">
-        <v>-7.47</v>
-      </c>
-      <c r="T27" t="n">
-        <v>4</v>
-      </c>
-      <c r="U27" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Carnival Cruise Line</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>suite</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>3</v>
-      </c>
-      <c r="G28" t="n">
-        <v>11</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>52</v>
-      </c>
-      <c r="O28" t="n">
-        <v>114</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v>0.2381</v>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="R28" t="n">
-        <v>-0.1741</v>
-      </c>
-      <c r="S28" t="n">
-        <v>-17.41</v>
-      </c>
-      <c r="T28" t="n">
-        <v>4</v>
-      </c>
-      <c r="U28" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Alaska</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>balcony</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
-        <v>10</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.0833</v>
-      </c>
-      <c r="S29" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2</v>
-      </c>
-      <c r="U29" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Alaska</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="n">
-        <v>10</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="S30" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2</v>
-      </c>
-      <c r="U30" s="9" t="inlineStr">
-        <is>
-          <t>VERY THIN (n=5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Alaska</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>oceanview</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="n">
-        <v>5</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J31" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="S31" t="n">
-        <v>-3.33</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" s="9" t="inlineStr">
-        <is>
-          <t>VERY THIN (n=5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Alaska</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>suite</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="6" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="R32" t="n">
-        <v>-0.1667</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" s="9" t="inlineStr">
-        <is>
-          <t>VERY THIN (n=5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>balcony</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>3</v>
-      </c>
-      <c r="G33" t="n">
-        <v>6</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="J33" s="6" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="K33" s="6" t="n">
-        <v>0.05556</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>6</v>
-      </c>
-      <c r="O33" t="n">
-        <v>10</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v>0.0833</v>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="R33" t="n">
-        <v>-0.0208</v>
-      </c>
-      <c r="S33" t="n">
-        <v>-18.75</v>
-      </c>
-      <c r="T33" t="n">
-        <v>4</v>
-      </c>
-      <c r="U33" s="9" t="inlineStr">
-        <is>
-          <t>VERY THIN (n=6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>3</v>
-      </c>
-      <c r="G34" t="n">
-        <v>6</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>4</v>
-      </c>
-      <c r="O34" t="n">
-        <v>10</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>-0.1667</v>
-      </c>
-      <c r="S34" t="n">
-        <v>-16.67</v>
-      </c>
-      <c r="T34" t="n">
-        <v>4</v>
-      </c>
-      <c r="U34" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (n=3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>oceanview</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>3</v>
-      </c>
-      <c r="G35" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>3</v>
-      </c>
-      <c r="O35" t="n">
-        <v>5</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>-0.1667</v>
-      </c>
-      <c r="S35" t="n">
-        <v>-16.67</v>
-      </c>
-      <c r="T35" t="n">
-        <v>4</v>
-      </c>
-      <c r="U35" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (n=3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>suite</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>6</v>
-      </c>
-      <c r="O36" t="n">
-        <v>5</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>-0.3333</v>
-      </c>
-      <c r="S36" t="n">
-        <v>-33.33</v>
-      </c>
-      <c r="T36" t="n">
-        <v>4</v>
-      </c>
-      <c r="U36" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (n=3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>balcony</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" t="n">
-        <v>38</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>16</v>
-      </c>
-      <c r="O37" t="n">
-        <v>122</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v>0.0185</v>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v>0.0063</v>
-      </c>
-      <c r="R37" t="n">
-        <v>-0.0123</v>
-      </c>
-      <c r="S37" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="T37" t="n">
-        <v>4</v>
-      </c>
-      <c r="U37" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=38)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>3</v>
-      </c>
-      <c r="G38" t="n">
-        <v>38</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>16</v>
-      </c>
-      <c r="O38" t="n">
-        <v>122</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>4</v>
-      </c>
-      <c r="U38" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>oceanview</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G39" t="n">
-        <v>19</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>8</v>
-      </c>
-      <c r="O39" t="n">
-        <v>61</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T39" t="n">
-        <v>4</v>
-      </c>
-      <c r="U39" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Caribbean</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>suite</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>3</v>
-      </c>
-      <c r="G40" t="n">
-        <v>31</v>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>13</v>
-      </c>
-      <c r="O40" t="n">
-        <v>109</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v>0.0682</v>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v>0.0071</v>
-      </c>
-      <c r="R40" t="n">
-        <v>-0.061</v>
-      </c>
-      <c r="S40" t="n">
-        <v>-6.1</v>
-      </c>
-      <c r="T40" t="n">
-        <v>4</v>
-      </c>
-      <c r="U40" s="9" t="inlineStr">
-        <is>
-          <t>ok (n=31)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Northern Europe</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>balcony</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>3</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="6" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="K41" s="6" t="n">
-        <v>-0.16667</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2</v>
-      </c>
-      <c r="O41" t="n">
-        <v>2</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="S41" t="n">
-        <v>25</v>
-      </c>
-      <c r="T41" t="n">
-        <v>4</v>
-      </c>
-      <c r="U41" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (n=2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Northern Europe</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>3</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>4</v>
-      </c>
-      <c r="U42" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (n=1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Northern Europe</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>oceanview</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>3</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>4</v>
-      </c>
-      <c r="U43" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (n=1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Northern Europe</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>suite</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>3</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>4</v>
-      </c>
-      <c r="U44" s="9" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (n=1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>balcony</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>3</v>
-      </c>
-      <c r="G45" t="n">
-        <v>14</v>
-      </c>
-      <c r="H45" s="6" t="n">
-        <v>0.2143</v>
-      </c>
-      <c r="I45" s="6" t="n">
-        <v>0.2857</v>
-      </c>
-      <c r="J45" s="6" t="n">
-        <v>0.07140000000000001</v>
-      </c>
-      <c r="K45" s="6" t="n">
-        <v>0.02381</v>
-      </c>
-      <c r="L45" t="n">
-        <v>2</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" t="n">
-        <v>14</v>
-      </c>
-      <c r="O45" t="n">
-        <v>8</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v>0.2143</v>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v>0.2273</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="S45" t="n">
-        <v>-5.84</v>
-      </c>
-      <c r="T45" t="n">
-        <v>4</v>
-      </c>
-      <c r="U45" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=14)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>inside</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>3</v>
-      </c>
-      <c r="G46" t="n">
-        <v>10</v>
-      </c>
-      <c r="H46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>9</v>
-      </c>
-      <c r="O46" t="n">
-        <v>6</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>4</v>
-      </c>
-      <c r="U46" s="9" t="inlineStr">
-        <is>
-          <t>VERY THIN (n=7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>oceanview</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>3</v>
-      </c>
-      <c r="G47" t="n">
-        <v>7</v>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>0.2857</v>
-      </c>
-      <c r="I47" s="6" t="n">
-        <v>0.2857</v>
-      </c>
-      <c r="J47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>7</v>
-      </c>
-      <c r="O47" t="n">
-        <v>4</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v>0.2857</v>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v>0.2727</v>
-      </c>
-      <c r="R47" t="n">
-        <v>-0.013</v>
-      </c>
-      <c r="S47" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="T47" t="n">
-        <v>4</v>
-      </c>
-      <c r="U47" s="9" t="inlineStr">
-        <is>
-          <t>VERY THIN (n=7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Norwegian Cruise Line</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Southern Europe</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>suite</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>3</v>
-      </c>
-      <c r="G48" t="n">
-        <v>11</v>
-      </c>
-      <c r="H48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>8</v>
-      </c>
-      <c r="O48" t="n">
-        <v>5</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>4</v>
-      </c>
-      <c r="U48" s="10" t="inlineStr">
-        <is>
-          <t>THIN (n=11)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A16:U48"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>